--- a/data/trans_orig/P19C09-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P19C09-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por otros motivos en 2007</t>
+          <t>Población según si el motivo por su última visita al dentista fue por otros motivos en 2007 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>944</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8909</t>
+          <t>9302</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>1821</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10411</t>
+          <t>10441</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3854</t>
+          <t>3698</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14844</t>
+          <t>15875</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>350492</t>
+          <t>350099</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>358473</t>
+          <t>358457</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>365841</t>
+          <t>365811</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>374392</t>
+          <t>374431</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>720809</t>
+          <t>719778</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>731799</t>
+          <t>731955</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6255</t>
+          <t>5663</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21697</t>
+          <t>21419</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7044</t>
+          <t>6955</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22030</t>
+          <t>22179</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15561</t>
+          <t>15938</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36774</t>
+          <t>36687</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>554084</t>
+          <t>554362</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>569526</t>
+          <t>570118</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>525678</t>
+          <t>525529</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>540664</t>
+          <t>540753</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1086715</t>
+          <t>1086802</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1107928</t>
+          <t>1107551</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>6826</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21358</t>
+          <t>21309</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6017</t>
+          <t>5764</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20142</t>
+          <t>19128</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15041</t>
+          <t>14825</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33873</t>
+          <t>34964</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>479652</t>
+          <t>479701</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>494325</t>
+          <t>494184</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>581387</t>
+          <t>582401</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>595512</t>
+          <t>595765</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1068666</t>
+          <t>1067575</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1087498</t>
+          <t>1087714</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>1989</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15649</t>
+          <t>15041</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8570</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23923</t>
+          <t>23904</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12735</t>
+          <t>13242</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32563</t>
+          <t>31959</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>389099</t>
+          <t>389707</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>402805</t>
+          <t>402759</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>415262</t>
+          <t>415281</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>430615</t>
+          <t>431014</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>811370</t>
+          <t>811974</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>831198</t>
+          <t>830691</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,43%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4786</t>
+          <t>4647</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17162</t>
+          <t>17342</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10683</t>
+          <t>11695</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27522</t>
+          <t>28079</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18917</t>
+          <t>19361</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39515</t>
+          <t>39378</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,69%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>254343</t>
+          <t>254163</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>266719</t>
+          <t>266858</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>289913</t>
+          <t>289356</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>306752</t>
+          <t>305740</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>549425</t>
+          <t>549562</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>570023</t>
+          <t>569579</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,71%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4604</t>
+          <t>4788</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16275</t>
+          <t>16515</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8527</t>
+          <t>8585</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22559</t>
+          <t>22406</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16010</t>
+          <t>15425</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>34868</t>
+          <t>32781</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>195006</t>
+          <t>194766</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>206677</t>
+          <t>206493</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>224379</t>
+          <t>224532</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>238411</t>
+          <t>238353</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>423351</t>
+          <t>425438</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>442209</t>
+          <t>442794</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,63%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>6432</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19632</t>
+          <t>19914</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4661</t>
+          <t>4613</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18172</t>
+          <t>18019</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13861</t>
+          <t>13443</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33444</t>
+          <t>32073</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>107132</t>
+          <t>106850</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>120357</t>
+          <t>120332</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>190036</t>
+          <t>190189</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>203547</t>
+          <t>203595</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>301528</t>
+          <t>302899</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>321111</t>
+          <t>321529</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,99%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>49747</t>
+          <t>49811</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>80395</t>
+          <t>80461</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>69534</t>
+          <t>68707</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>106829</t>
+          <t>105070</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>126092</t>
+          <t>127168</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>178096</t>
+          <t>175380</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2370096</t>
+          <t>2370030</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2400744</t>
+          <t>2400680</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2630426</t>
+          <t>2632185</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2667721</t>
+          <t>2668548</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5009649</t>
+          <t>5012365</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5061653</t>
+          <t>5060577</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,55%</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por otros motivos en 2012</t>
+          <t>Población según si el motivo por su última visita al dentista fue por otros motivos en 2012 (tasa de respuesta: 97,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3687</t>
+          <t>3152</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14579</t>
+          <t>14001</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5581</t>
+          <t>5942</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19057</t>
+          <t>20823</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12630</t>
+          <t>11668</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29298</t>
+          <t>28555</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>351593</t>
+          <t>352171</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>362485</t>
+          <t>363020</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>342242</t>
+          <t>340476</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>355718</t>
+          <t>355357</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>698173</t>
+          <t>698916</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>714841</t>
+          <t>715803</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5618</t>
+          <t>5690</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20081</t>
+          <t>19675</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11896</t>
+          <t>11377</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29004</t>
+          <t>29442</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19795</t>
+          <t>20256</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43109</t>
+          <t>42748</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>569242</t>
+          <t>569648</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>583705</t>
+          <t>583633</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>512573</t>
+          <t>512135</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>529681</t>
+          <t>530200</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1087790</t>
+          <t>1088151</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1111104</t>
+          <t>1110643</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,21%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2946</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16726</t>
+          <t>16915</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8610</t>
+          <t>8743</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28251</t>
+          <t>27875</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14463</t>
+          <t>14427</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37068</t>
+          <t>36847</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>554376</t>
+          <t>554187</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>568156</t>
+          <t>567971</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>614969</t>
+          <t>615345</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>634610</t>
+          <t>634477</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1177254</t>
+          <t>1177475</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1199859</t>
+          <t>1199895</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>2086</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12403</t>
+          <t>12183</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4625</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18855</t>
+          <t>19357</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8461</t>
+          <t>8862</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25899</t>
+          <t>26448</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>508477</t>
+          <t>508697</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>517988</t>
+          <t>518794</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>528026</t>
+          <t>527524</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>542445</t>
+          <t>542256</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1041861</t>
+          <t>1041312</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1059299</t>
+          <t>1058898</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2051</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11411</t>
+          <t>12291</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3998</t>
+          <t>4053</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16706</t>
+          <t>17480</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>8943</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24663</t>
+          <t>23782</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>337736</t>
+          <t>336856</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>347145</t>
+          <t>347096</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>365749</t>
+          <t>364975</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>378457</t>
+          <t>378402</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>706939</t>
+          <t>707820</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>722731</t>
+          <t>722659</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4229</t>
+          <t>4899</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18766</t>
+          <t>21586</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2944</t>
+          <t>2967</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13921</t>
+          <t>13628</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9410</t>
+          <t>10102</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28382</t>
+          <t>28226</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>242612</t>
+          <t>239792</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>257149</t>
+          <t>256479</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>282745</t>
+          <t>283038</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>293722</t>
+          <t>293699</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>529662</t>
+          <t>529818</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>548634</t>
+          <t>547942</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,19%</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4734</t>
+          <t>5221</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7384</t>
+          <t>7977</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24241</t>
+          <t>23744</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8343</t>
+          <t>8367</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23851</t>
+          <t>24187</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -5882,7 +5882,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>173984</t>
+          <t>173497</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>273845</t>
+          <t>274342</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>290702</t>
+          <t>290109</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>452953</t>
+          <t>452617</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>468461</t>
+          <t>468437</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5967,7 +5967,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>35840</t>
+          <t>34584</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>65963</t>
+          <t>63186</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>68765</t>
+          <t>66714</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>106697</t>
+          <t>105433</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>114248</t>
+          <t>111290</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>163248</t>
+          <t>159439</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2770756</t>
+          <t>2773533</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2800879</t>
+          <t>2802135</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2963487</t>
+          <t>2964751</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3001419</t>
+          <t>3003470</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5743655</t>
+          <t>5747464</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5792655</t>
+          <t>5795613</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,12%</t>
         </is>
       </c>
     </row>
@@ -6495,7 +6495,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por otros motivos en 2016</t>
+          <t>Población según si el motivo por su última visita al dentista fue por otros motivos en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6690,12 +6690,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6436</t>
+          <t>6478</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20452</t>
+          <t>20372</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3741</t>
+          <t>3002</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14131</t>
+          <t>14398</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6760,12 +6760,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12083</t>
+          <t>12008</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29286</t>
+          <t>30196</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -6803,12 +6803,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>332388</t>
+          <t>332468</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>346404</t>
+          <t>346362</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6818,12 +6818,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6838,12 +6838,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>337799</t>
+          <t>337532</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>348189</t>
+          <t>348928</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6853,12 +6853,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6873,12 +6873,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>675484</t>
+          <t>674574</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>692687</t>
+          <t>692762</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,3%</t>
         </is>
       </c>
     </row>
@@ -7033,12 +7033,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8575</t>
+          <t>8788</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24826</t>
+          <t>24786</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7048,7 +7048,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9307</t>
+          <t>9794</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26065</t>
+          <t>25717</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7103,12 +7103,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20902</t>
+          <t>21904</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43334</t>
+          <t>43844</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -7146,12 +7146,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>468252</t>
+          <t>468292</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>484503</t>
+          <t>484290</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>470655</t>
+          <t>471003</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>487413</t>
+          <t>486926</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7216,12 +7216,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>946463</t>
+          <t>945953</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>968895</t>
+          <t>967893</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,79%</t>
         </is>
       </c>
     </row>
@@ -7376,12 +7376,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11745</t>
+          <t>11510</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30641</t>
+          <t>30269</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7391,12 +7391,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7411,12 +7411,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6890</t>
+          <t>6398</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21754</t>
+          <t>20763</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7426,12 +7426,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7446,12 +7446,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21523</t>
+          <t>20895</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43163</t>
+          <t>43051</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -7489,12 +7489,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>527219</t>
+          <t>527591</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>546115</t>
+          <t>546350</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>551326</t>
+          <t>552317</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>566190</t>
+          <t>566682</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7559,12 +7559,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1087777</t>
+          <t>1087889</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1109417</t>
+          <t>1110045</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
@@ -7719,12 +7719,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5235</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19027</t>
+          <t>19935</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7734,12 +7734,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7312</t>
+          <t>6505</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23170</t>
+          <t>21800</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7769,12 +7769,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7789,12 +7789,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15239</t>
+          <t>16231</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37705</t>
+          <t>36825</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7804,12 +7804,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -7832,12 +7832,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>493345</t>
+          <t>492437</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>507137</t>
+          <t>507101</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7847,12 +7847,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>521714</t>
+          <t>523084</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>537572</t>
+          <t>538379</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7882,12 +7882,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7902,12 +7902,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1019551</t>
+          <t>1020431</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1042017</t>
+          <t>1041025</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7917,12 +7917,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,46%</t>
         </is>
       </c>
     </row>
@@ -8062,12 +8062,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2286</t>
+          <t>2592</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13681</t>
+          <t>13485</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7907</t>
+          <t>8697</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24610</t>
+          <t>24953</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8112,12 +8112,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8132,12 +8132,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12874</t>
+          <t>13808</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32753</t>
+          <t>32878</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8147,12 +8147,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -8175,12 +8175,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>357321</t>
+          <t>357517</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>368716</t>
+          <t>368410</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8190,12 +8190,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>371263</t>
+          <t>370920</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>387966</t>
+          <t>387176</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8225,12 +8225,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8245,12 +8245,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>734122</t>
+          <t>733997</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>754001</t>
+          <t>753067</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8260,12 +8260,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,2%</t>
         </is>
       </c>
     </row>
@@ -8405,12 +8405,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1892</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>10467</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8420,12 +8420,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2038</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11721</t>
+          <t>12684</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8455,12 +8455,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8475,12 +8475,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5719</t>
+          <t>5804</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18459</t>
+          <t>19456</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8490,12 +8490,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -8518,12 +8518,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>219537</t>
+          <t>219658</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>228233</t>
+          <t>228271</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8533,12 +8533,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>265227</t>
+          <t>264264</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>274930</t>
+          <t>274910</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8588,12 +8588,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>488615</t>
+          <t>487618</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>501355</t>
+          <t>501270</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8603,12 +8603,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -8748,12 +8748,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4170</t>
+          <t>4204</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15696</t>
+          <t>15014</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8763,12 +8763,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>1837</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14817</t>
+          <t>14920</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8798,12 +8798,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8818,12 +8818,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7826</t>
+          <t>7832</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24167</t>
+          <t>24294</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8838,7 +8838,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -8861,12 +8861,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>131361</t>
+          <t>132043</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>142887</t>
+          <t>142853</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8876,12 +8876,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>213062</t>
+          <t>212959</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>225883</t>
+          <t>226042</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8911,12 +8911,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8931,12 +8931,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>350769</t>
+          <t>350642</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>367110</t>
+          <t>367104</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8946,7 +8946,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -9091,12 +9091,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>61151</t>
+          <t>61511</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>96900</t>
+          <t>96961</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -9126,12 +9126,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>59388</t>
+          <t>59852</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>95811</t>
+          <t>96283</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9141,12 +9141,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9161,12 +9161,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>128980</t>
+          <t>130042</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>177268</t>
+          <t>179356</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9176,12 +9176,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -9204,12 +9204,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2567433</t>
+          <t>2567372</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2603182</t>
+          <t>2602822</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9239,12 +9239,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2771504</t>
+          <t>2771032</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2807927</t>
+          <t>2807463</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9254,12 +9254,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9274,12 +9274,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5354380</t>
+          <t>5352292</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5402668</t>
+          <t>5401606</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9289,12 +9289,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,65%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19C09-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P19C09-Edad-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>914</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9302</t>
+          <t>8284</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1821</t>
+          <t>1829</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10441</t>
+          <t>11301</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3698</t>
+          <t>3737</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15875</t>
+          <t>15326</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>350099</t>
+          <t>351117</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>358457</t>
+          <t>358487</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>365811</t>
+          <t>364951</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>374431</t>
+          <t>374423</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>719778</t>
+          <t>720327</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>731955</t>
+          <t>731916</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,49%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5663</t>
+          <t>5596</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21419</t>
+          <t>21298</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6955</t>
+          <t>6758</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22179</t>
+          <t>21098</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15938</t>
+          <t>15153</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36687</t>
+          <t>37122</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>554362</t>
+          <t>554483</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>570118</t>
+          <t>570185</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>525529</t>
+          <t>526610</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>540753</t>
+          <t>540950</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1086802</t>
+          <t>1086367</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1107551</t>
+          <t>1108336</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6826</t>
+          <t>6668</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21309</t>
+          <t>21887</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5764</t>
+          <t>5228</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19128</t>
+          <t>19869</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14825</t>
+          <t>15403</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34964</t>
+          <t>34183</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>479701</t>
+          <t>479123</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>494184</t>
+          <t>494342</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>582401</t>
+          <t>581660</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>595765</t>
+          <t>596301</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1067575</t>
+          <t>1068356</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1087714</t>
+          <t>1087136</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,6%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>2485</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15041</t>
+          <t>15744</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8171</t>
+          <t>8537</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23904</t>
+          <t>24772</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13242</t>
+          <t>13176</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31959</t>
+          <t>32076</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>389707</t>
+          <t>389004</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>402759</t>
+          <t>402263</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>415281</t>
+          <t>414413</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>431014</t>
+          <t>430648</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>811974</t>
+          <t>811857</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>830691</t>
+          <t>830757</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,44%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4647</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17342</t>
+          <t>16225</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11695</t>
+          <t>11526</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28079</t>
+          <t>27896</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19361</t>
+          <t>19011</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39378</t>
+          <t>38969</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>254163</t>
+          <t>255280</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>266858</t>
+          <t>266829</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>289356</t>
+          <t>289539</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>305740</t>
+          <t>305909</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>549562</t>
+          <t>549971</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>569579</t>
+          <t>569929</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,77%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4788</t>
+          <t>4556</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16515</t>
+          <t>16143</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8585</t>
+          <t>8381</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22406</t>
+          <t>22939</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15425</t>
+          <t>16174</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32781</t>
+          <t>33725</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>194766</t>
+          <t>195138</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>206493</t>
+          <t>206725</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>224532</t>
+          <t>223999</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>238353</t>
+          <t>238557</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>425438</t>
+          <t>424494</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>442794</t>
+          <t>442045</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,47%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6432</t>
+          <t>6362</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19914</t>
+          <t>20115</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4613</t>
+          <t>4597</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18019</t>
+          <t>18029</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13443</t>
+          <t>13792</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>32073</t>
+          <t>32585</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>106850</t>
+          <t>106649</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>120332</t>
+          <t>120402</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>190189</t>
+          <t>190179</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>203595</t>
+          <t>203611</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>302899</t>
+          <t>302387</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>321529</t>
+          <t>321180</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,88%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>49811</t>
+          <t>49727</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>80461</t>
+          <t>81908</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>68707</t>
+          <t>69568</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>105070</t>
+          <t>105202</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>127168</t>
+          <t>126470</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>175380</t>
+          <t>175335</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2370030</t>
+          <t>2368583</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2400680</t>
+          <t>2400764</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2632185</t>
+          <t>2632053</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2668548</t>
+          <t>2667687</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5012365</t>
+          <t>5012410</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5060577</t>
+          <t>5061275</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,56%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3152</t>
+          <t>3753</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14001</t>
+          <t>14411</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5942</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20823</t>
+          <t>19369</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11668</t>
+          <t>11810</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28555</t>
+          <t>28146</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>352171</t>
+          <t>351761</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>363020</t>
+          <t>362419</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>340476</t>
+          <t>341930</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>355357</t>
+          <t>355294</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>698916</t>
+          <t>699325</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>715803</t>
+          <t>715661</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5690</t>
+          <t>5662</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19675</t>
+          <t>19815</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11377</t>
+          <t>11507</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29442</t>
+          <t>29748</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20256</t>
+          <t>19295</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>42748</t>
+          <t>43427</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>569648</t>
+          <t>569508</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>583633</t>
+          <t>583661</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>512135</t>
+          <t>511829</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>530200</t>
+          <t>530070</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1088151</t>
+          <t>1087472</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1110643</t>
+          <t>1111604</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,29%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3131</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16915</t>
+          <t>14967</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8743</t>
+          <t>9174</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27875</t>
+          <t>29025</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14427</t>
+          <t>15042</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36847</t>
+          <t>38556</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>554187</t>
+          <t>556135</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>567971</t>
+          <t>568211</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>615345</t>
+          <t>614195</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>634477</t>
+          <t>634046</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1177475</t>
+          <t>1175766</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1199895</t>
+          <t>1199280</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2086</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12183</t>
+          <t>12414</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4625</t>
+          <t>4493</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19357</t>
+          <t>20329</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8862</t>
+          <t>8846</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26448</t>
+          <t>25679</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>508697</t>
+          <t>508466</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>518794</t>
+          <t>518781</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>527524</t>
+          <t>526552</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>542256</t>
+          <t>542388</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1041312</t>
+          <t>1042081</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1058898</t>
+          <t>1058914</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12291</t>
+          <t>12141</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4053</t>
+          <t>3814</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17480</t>
+          <t>17071</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8943</t>
+          <t>8812</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23782</t>
+          <t>25455</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>336856</t>
+          <t>337006</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>347096</t>
+          <t>347112</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>364975</t>
+          <t>365384</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>378402</t>
+          <t>378641</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>707820</t>
+          <t>706147</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>722659</t>
+          <t>722790</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4899</t>
+          <t>4986</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21586</t>
+          <t>20217</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2967</t>
+          <t>2951</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13628</t>
+          <t>12999</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10102</t>
+          <t>9984</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28226</t>
+          <t>28030</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>239792</t>
+          <t>241161</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>256479</t>
+          <t>256392</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>283038</t>
+          <t>283667</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>293699</t>
+          <t>293715</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>529818</t>
+          <t>530014</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>547942</t>
+          <t>548060</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,21%</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5221</t>
+          <t>6358</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7977</t>
+          <t>8292</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23744</t>
+          <t>23846</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8367</t>
+          <t>8282</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24187</t>
+          <t>24434</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -5882,7 +5882,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>173497</t>
+          <t>172360</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>274342</t>
+          <t>274240</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>290109</t>
+          <t>289794</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>452617</t>
+          <t>452370</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>468437</t>
+          <t>468522</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,26%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>34584</t>
+          <t>36997</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>63186</t>
+          <t>66974</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>66714</t>
+          <t>69078</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>105433</t>
+          <t>106971</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>111290</t>
+          <t>111187</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>159439</t>
+          <t>160618</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2773533</t>
+          <t>2769745</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2802135</t>
+          <t>2799722</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2964751</t>
+          <t>2963213</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3003470</t>
+          <t>3001106</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5747464</t>
+          <t>5746285</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5795613</t>
+          <t>5795716</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6478</t>
+          <t>6288</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20372</t>
+          <t>21532</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3002</t>
+          <t>3750</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14398</t>
+          <t>15218</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6760,12 +6760,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12008</t>
+          <t>11988</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30196</t>
+          <t>30191</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6803,12 +6803,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>332468</t>
+          <t>331308</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>346362</t>
+          <t>346552</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6818,12 +6818,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6838,12 +6838,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>337532</t>
+          <t>336712</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>348928</t>
+          <t>348180</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6853,12 +6853,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6873,12 +6873,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>674574</t>
+          <t>674579</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>692762</t>
+          <t>692782</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8788</t>
+          <t>8701</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24786</t>
+          <t>24389</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9794</t>
+          <t>9477</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25717</t>
+          <t>25945</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7103,12 +7103,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21904</t>
+          <t>21911</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43844</t>
+          <t>44898</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -7146,12 +7146,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>468292</t>
+          <t>468689</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>484290</t>
+          <t>484377</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>471003</t>
+          <t>470775</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>486926</t>
+          <t>487243</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7216,12 +7216,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>945953</t>
+          <t>944899</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>967893</t>
+          <t>967886</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7376,12 +7376,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11510</t>
+          <t>10839</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30269</t>
+          <t>30361</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7391,12 +7391,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7411,12 +7411,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6398</t>
+          <t>6492</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20763</t>
+          <t>21063</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7426,12 +7426,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7446,12 +7446,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20895</t>
+          <t>21469</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43051</t>
+          <t>43503</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -7489,12 +7489,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>527591</t>
+          <t>527499</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>546350</t>
+          <t>547021</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>552317</t>
+          <t>552017</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>566682</t>
+          <t>566588</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7559,12 +7559,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1087889</t>
+          <t>1087437</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1110045</t>
+          <t>1109471</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,1%</t>
         </is>
       </c>
     </row>
@@ -7719,12 +7719,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>5223</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19935</t>
+          <t>18995</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7734,12 +7734,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6505</t>
+          <t>7326</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21800</t>
+          <t>23259</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7769,12 +7769,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7789,12 +7789,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16231</t>
+          <t>15436</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36825</t>
+          <t>34985</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7804,12 +7804,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -7832,12 +7832,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>492437</t>
+          <t>493377</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>507101</t>
+          <t>507149</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7847,12 +7847,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>523084</t>
+          <t>521625</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>538379</t>
+          <t>537558</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7882,12 +7882,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7902,12 +7902,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1020431</t>
+          <t>1022271</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1041025</t>
+          <t>1041820</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7917,12 +7917,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -8062,12 +8062,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2592</t>
+          <t>3208</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13485</t>
+          <t>14131</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8697</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24953</t>
+          <t>24810</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8112,12 +8112,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8132,12 +8132,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13808</t>
+          <t>13087</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32878</t>
+          <t>32670</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8147,12 +8147,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -8175,12 +8175,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>357517</t>
+          <t>356871</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>368410</t>
+          <t>367794</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8190,12 +8190,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>370920</t>
+          <t>371063</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>387176</t>
+          <t>387232</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8225,12 +8225,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8245,12 +8245,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>733997</t>
+          <t>734205</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>753067</t>
+          <t>753788</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8260,12 +8260,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,29%</t>
         </is>
       </c>
     </row>
@@ -8405,12 +8405,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1854</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10467</t>
+          <t>11155</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8425,7 +8425,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>2109</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12684</t>
+          <t>12541</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8455,12 +8455,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8475,12 +8475,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5804</t>
+          <t>5572</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19456</t>
+          <t>17807</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8490,12 +8490,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -8518,12 +8518,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>219658</t>
+          <t>218970</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>228271</t>
+          <t>228255</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>264264</t>
+          <t>264407</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>274910</t>
+          <t>274839</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8588,12 +8588,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>487618</t>
+          <t>489267</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>501270</t>
+          <t>501502</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8603,12 +8603,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -8748,12 +8748,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4204</t>
+          <t>4169</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15014</t>
+          <t>15398</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8763,12 +8763,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1837</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14920</t>
+          <t>14902</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8798,47 +8798,47 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
+          <t>6,54%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>14067</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>7710</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>24571</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>3,75%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
           <t>6,55%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>14067</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>7832</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>24294</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>3,75%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -8861,12 +8861,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>132043</t>
+          <t>131659</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>142853</t>
+          <t>142888</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8876,12 +8876,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>212959</t>
+          <t>212977</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>226042</t>
+          <t>225888</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8911,47 +8911,47 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
+          <t>93,46%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>99,13%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>360869</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>350365</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>367226</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>96,25%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>93,45%</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>99,19%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>360869</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>350642</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>367104</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>96,25%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>93,52%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -9091,12 +9091,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>61511</t>
+          <t>60098</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>96961</t>
+          <t>94125</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9126,12 +9126,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>59852</t>
+          <t>61045</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>96283</t>
+          <t>97964</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9141,12 +9141,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9161,12 +9161,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>130042</t>
+          <t>130383</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>179356</t>
+          <t>180676</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9176,12 +9176,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -9204,12 +9204,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2567372</t>
+          <t>2570208</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2602822</t>
+          <t>2604235</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9239,12 +9239,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2771032</t>
+          <t>2769351</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2807463</t>
+          <t>2806270</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9254,12 +9254,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9274,12 +9274,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5352292</t>
+          <t>5350972</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5401606</t>
+          <t>5401265</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9289,12 +9289,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,64%</t>
         </is>
       </c>
     </row>
